--- a/Data/EXCEL/Transfer/salemon/202206/2254-salemon-202206.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202206/2254-salemon-202206.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25330"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\linea\OneDrive\myStocksPGMs\V2.0\xls2xlsx\transfer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORKSPACES\myStocksPGMs\V2.0\xls2xlsx\transfer\202206\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13DA2C65-056D-4411-AB0B-A376F301B6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0D56D38-8557-4699-AB4A-86F76CD0877F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3285" yWindow="2625" windowWidth="24465" windowHeight="12855"/>
+    <workbookView xWindow="945" yWindow="3600" windowWidth="26925" windowHeight="11205"/>
   </bookViews>
   <sheets>
     <sheet name="2254-salemon-202206" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -1218,15 +1218,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q14"/>
+  <dimension ref="A1:Q15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="5" width="10.875" customWidth="1"/>
-    <col min="6" max="6" width="10.375" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="16" width="10.875" customWidth="1"/>
-    <col min="17" max="17" width="12.75" customWidth="1"/>
+    <col min="1" max="1" width="14.875" customWidth="1"/>
+    <col min="2" max="5" width="12.5" customWidth="1"/>
+    <col min="6" max="6" width="11.875" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="16" width="12.5" customWidth="1"/>
+    <col min="17" max="17" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
@@ -1379,431 +1379,431 @@
     </row>
     <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>44682</v>
+        <v>44713</v>
       </c>
       <c r="B5" s="7">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="C5" s="7">
-        <v>280</v>
+        <v>246.5</v>
       </c>
       <c r="D5" s="7">
-        <v>285.5</v>
+        <v>279.5</v>
       </c>
       <c r="E5" s="7">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="F5" s="8">
-        <v>21</v>
+        <v>-33.5</v>
       </c>
       <c r="G5" s="8">
-        <v>8.11</v>
+        <v>-11.96</v>
       </c>
       <c r="H5" s="9">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="I5" s="8">
-        <v>121.2</v>
-      </c>
-      <c r="J5" s="8">
-        <v>139.80000000000001</v>
+        <v>-15.4</v>
+      </c>
+      <c r="J5" s="10">
+        <v>23.1</v>
       </c>
       <c r="K5" s="9">
-        <v>5.07</v>
-      </c>
-      <c r="L5" s="8">
-        <v>67.099999999999994</v>
+        <v>6.53</v>
+      </c>
+      <c r="L5" s="10">
+        <v>54.8</v>
       </c>
       <c r="M5" s="9">
-        <v>1.72</v>
+        <v>1.46</v>
       </c>
       <c r="N5" s="8">
-        <v>121.2</v>
-      </c>
-      <c r="O5" s="8">
-        <v>139.80000000000001</v>
+        <v>-15.4</v>
+      </c>
+      <c r="O5" s="10">
+        <v>23.1</v>
       </c>
       <c r="P5" s="9">
-        <v>5.07</v>
-      </c>
-      <c r="Q5" s="8">
-        <v>67.099999999999994</v>
+        <v>6.53</v>
+      </c>
+      <c r="Q5" s="10">
+        <v>54.8</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>44652</v>
+        <v>44682</v>
       </c>
       <c r="B6" s="7">
-        <v>261.5</v>
+        <v>259</v>
       </c>
       <c r="C6" s="7">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="D6" s="7">
-        <v>263</v>
+        <v>285.5</v>
       </c>
       <c r="E6" s="7">
-        <v>248.5</v>
+        <v>226</v>
       </c>
       <c r="F6" s="10">
-        <v>-2.5</v>
+        <v>21</v>
       </c>
       <c r="G6" s="10">
-        <v>-0.96</v>
+        <v>8.11</v>
       </c>
       <c r="H6" s="9">
-        <v>0.77900000000000003</v>
+        <v>1.72</v>
       </c>
       <c r="I6" s="10">
-        <v>-10</v>
+        <v>121.2</v>
       </c>
       <c r="J6" s="10">
-        <v>-19.5</v>
+        <v>139.80000000000001</v>
       </c>
       <c r="K6" s="9">
-        <v>3.35</v>
-      </c>
-      <c r="L6" s="8">
-        <v>44.6</v>
+        <v>5.07</v>
+      </c>
+      <c r="L6" s="10">
+        <v>67.099999999999994</v>
       </c>
       <c r="M6" s="9">
-        <v>0.77900000000000003</v>
+        <v>1.72</v>
       </c>
       <c r="N6" s="10">
-        <v>-10</v>
+        <v>121.2</v>
       </c>
       <c r="O6" s="10">
-        <v>-19.5</v>
+        <v>139.80000000000001</v>
       </c>
       <c r="P6" s="9">
-        <v>3.35</v>
-      </c>
-      <c r="Q6" s="8">
-        <v>44.6</v>
+        <v>5.07</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>67.099999999999994</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>44621</v>
+        <v>44652</v>
       </c>
       <c r="B7" s="7">
-        <v>192.5</v>
+        <v>261.5</v>
       </c>
       <c r="C7" s="7">
-        <v>261.5</v>
+        <v>259</v>
       </c>
       <c r="D7" s="7">
-        <v>273.5</v>
+        <v>263</v>
       </c>
       <c r="E7" s="7">
-        <v>182</v>
+        <v>248.5</v>
       </c>
       <c r="F7" s="8">
-        <v>69</v>
+        <v>-2.5</v>
       </c>
       <c r="G7" s="8">
-        <v>35.840000000000003</v>
+        <v>-0.96</v>
       </c>
       <c r="H7" s="9">
-        <v>0.86599999999999999</v>
+        <v>0.77900000000000003</v>
       </c>
       <c r="I7" s="8">
-        <v>21.6</v>
+        <v>-10</v>
       </c>
       <c r="J7" s="8">
-        <v>41.6</v>
+        <v>-19.5</v>
       </c>
       <c r="K7" s="9">
-        <v>2.57</v>
-      </c>
-      <c r="L7" s="8">
-        <v>90.6</v>
+        <v>3.35</v>
+      </c>
+      <c r="L7" s="10">
+        <v>44.6</v>
       </c>
       <c r="M7" s="9">
-        <v>0.86599999999999999</v>
+        <v>0.77900000000000003</v>
       </c>
       <c r="N7" s="8">
-        <v>21.6</v>
+        <v>-10</v>
       </c>
       <c r="O7" s="8">
-        <v>41.6</v>
+        <v>-19.5</v>
       </c>
       <c r="P7" s="9">
-        <v>2.57</v>
-      </c>
-      <c r="Q7" s="8">
-        <v>90.6</v>
+        <v>3.35</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>44.6</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>44593</v>
+        <v>44621</v>
       </c>
       <c r="B8" s="7">
-        <v>193.5</v>
+        <v>192.5</v>
       </c>
       <c r="C8" s="7">
-        <v>192.5</v>
+        <v>261.5</v>
       </c>
       <c r="D8" s="7">
-        <v>194.5</v>
+        <v>273.5</v>
       </c>
       <c r="E8" s="7">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F8" s="10">
-        <v>-1</v>
+        <v>69</v>
       </c>
       <c r="G8" s="10">
-        <v>-0.52</v>
+        <v>35.840000000000003</v>
       </c>
       <c r="H8" s="9">
-        <v>0.71199999999999997</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="I8" s="10">
-        <v>-28.4</v>
-      </c>
-      <c r="J8" s="8">
-        <v>105.2</v>
+        <v>21.6</v>
+      </c>
+      <c r="J8" s="10">
+        <v>41.6</v>
       </c>
       <c r="K8" s="9">
-        <v>1.71</v>
-      </c>
-      <c r="L8" s="8">
-        <v>131.30000000000001</v>
+        <v>2.57</v>
+      </c>
+      <c r="L8" s="10">
+        <v>90.6</v>
       </c>
       <c r="M8" s="9">
-        <v>0.71199999999999997</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="N8" s="10">
-        <v>-28.4</v>
-      </c>
-      <c r="O8" s="8">
-        <v>105.2</v>
+        <v>21.6</v>
+      </c>
+      <c r="O8" s="10">
+        <v>41.6</v>
       </c>
       <c r="P8" s="9">
-        <v>1.71</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>131.30000000000001</v>
+        <v>2.57</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>90.6</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>44562</v>
+        <v>44593</v>
       </c>
       <c r="B9" s="7">
-        <v>185</v>
+        <v>193.5</v>
       </c>
       <c r="C9" s="7">
-        <v>193.5</v>
+        <v>192.5</v>
       </c>
       <c r="D9" s="7">
-        <v>193.5</v>
+        <v>194.5</v>
       </c>
       <c r="E9" s="7">
-        <v>177.5</v>
+        <v>181</v>
       </c>
       <c r="F9" s="8">
-        <v>8.5</v>
+        <v>-1</v>
       </c>
       <c r="G9" s="8">
-        <v>4.59</v>
+        <v>-0.52</v>
       </c>
       <c r="H9" s="9">
-        <v>0.99399999999999999</v>
-      </c>
-      <c r="I9" s="10">
-        <v>-17</v>
-      </c>
-      <c r="J9" s="8">
-        <v>154.6</v>
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="I9" s="8">
+        <v>-28.4</v>
+      </c>
+      <c r="J9" s="10">
+        <v>105.2</v>
       </c>
       <c r="K9" s="9">
-        <v>0.99399999999999999</v>
-      </c>
-      <c r="L9" s="8">
-        <v>154.6</v>
+        <v>1.71</v>
+      </c>
+      <c r="L9" s="10">
+        <v>131.30000000000001</v>
       </c>
       <c r="M9" s="9">
-        <v>0.99399999999999999</v>
-      </c>
-      <c r="N9" s="10">
-        <v>-17</v>
-      </c>
-      <c r="O9" s="8">
-        <v>154.6</v>
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="N9" s="8">
+        <v>-28.4</v>
+      </c>
+      <c r="O9" s="10">
+        <v>105.2</v>
       </c>
       <c r="P9" s="9">
-        <v>0.99399999999999999</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>154.6</v>
+        <v>1.71</v>
+      </c>
+      <c r="Q9" s="10">
+        <v>131.30000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>44531</v>
+        <v>44562</v>
       </c>
       <c r="B10" s="7">
-        <v>165.5</v>
+        <v>185</v>
       </c>
       <c r="C10" s="7">
-        <v>185</v>
+        <v>193.5</v>
       </c>
       <c r="D10" s="7">
-        <v>200</v>
+        <v>193.5</v>
       </c>
       <c r="E10" s="7">
-        <v>160.5</v>
-      </c>
-      <c r="F10" s="8">
-        <v>19.5</v>
-      </c>
-      <c r="G10" s="8">
-        <v>11.78</v>
+        <v>177.5</v>
+      </c>
+      <c r="F10" s="10">
+        <v>8.5</v>
+      </c>
+      <c r="G10" s="10">
+        <v>4.59</v>
       </c>
       <c r="H10" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="I10" s="10">
-        <v>-12.4</v>
-      </c>
-      <c r="J10" s="8">
-        <v>66.900000000000006</v>
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="I10" s="8">
+        <v>-17</v>
+      </c>
+      <c r="J10" s="10">
+        <v>154.6</v>
       </c>
       <c r="K10" s="9">
-        <v>11.6</v>
-      </c>
-      <c r="L10" s="8">
-        <v>63.8</v>
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="L10" s="10">
+        <v>154.6</v>
       </c>
       <c r="M10" s="9">
-        <v>1.2</v>
-      </c>
-      <c r="N10" s="10">
-        <v>-12.4</v>
-      </c>
-      <c r="O10" s="8">
-        <v>66.900000000000006</v>
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="N10" s="8">
+        <v>-17</v>
+      </c>
+      <c r="O10" s="10">
+        <v>154.6</v>
       </c>
       <c r="P10" s="9">
-        <v>11.6</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>63.8</v>
+        <v>0.99399999999999999</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>154.6</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>44501</v>
+        <v>44531</v>
       </c>
       <c r="B11" s="7">
-        <v>217</v>
+        <v>165.5</v>
       </c>
       <c r="C11" s="7">
-        <v>165.5</v>
+        <v>185</v>
       </c>
       <c r="D11" s="7">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="E11" s="7">
-        <v>159.5</v>
+        <v>160.5</v>
       </c>
       <c r="F11" s="10">
-        <v>-51.5</v>
+        <v>19.5</v>
       </c>
       <c r="G11" s="10">
-        <v>-23.73</v>
+        <v>11.78</v>
       </c>
       <c r="H11" s="9">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="I11" s="8">
-        <v>4.68</v>
-      </c>
-      <c r="J11" s="8">
-        <v>132.1</v>
+        <v>-12.4</v>
+      </c>
+      <c r="J11" s="10">
+        <v>66.900000000000006</v>
       </c>
       <c r="K11" s="9">
-        <v>10.4</v>
-      </c>
-      <c r="L11" s="8">
-        <v>63.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="L11" s="10">
+        <v>63.8</v>
       </c>
       <c r="M11" s="9">
-        <v>1.37</v>
+        <v>1.2</v>
       </c>
       <c r="N11" s="8">
-        <v>4.68</v>
-      </c>
-      <c r="O11" s="8">
-        <v>132.1</v>
+        <v>-12.4</v>
+      </c>
+      <c r="O11" s="10">
+        <v>66.900000000000006</v>
       </c>
       <c r="P11" s="9">
-        <v>10.4</v>
-      </c>
-      <c r="Q11" s="8">
-        <v>63.4</v>
+        <v>11.6</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>63.8</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>44470</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>17</v>
+        <v>44501</v>
+      </c>
+      <c r="B12" s="7">
+        <v>217</v>
+      </c>
+      <c r="C12" s="7">
+        <v>165.5</v>
+      </c>
+      <c r="D12" s="7">
+        <v>234</v>
+      </c>
+      <c r="E12" s="7">
+        <v>159.5</v>
+      </c>
+      <c r="F12" s="8">
+        <v>-51.5</v>
+      </c>
+      <c r="G12" s="8">
+        <v>-23.73</v>
       </c>
       <c r="H12" s="9">
-        <v>1.3</v>
-      </c>
-      <c r="I12" s="8">
-        <v>3.56</v>
-      </c>
-      <c r="J12" s="8">
-        <v>42</v>
+        <v>1.37</v>
+      </c>
+      <c r="I12" s="10">
+        <v>4.68</v>
+      </c>
+      <c r="J12" s="10">
+        <v>132.1</v>
       </c>
       <c r="K12" s="9">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="L12" s="8">
-        <v>56.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="L12" s="10">
+        <v>63.4</v>
       </c>
       <c r="M12" s="9">
-        <v>1.3</v>
-      </c>
-      <c r="N12" s="8">
-        <v>3.56</v>
-      </c>
-      <c r="O12" s="8">
-        <v>42</v>
+        <v>1.37</v>
+      </c>
+      <c r="N12" s="10">
+        <v>4.68</v>
+      </c>
+      <c r="O12" s="10">
+        <v>132.1</v>
       </c>
       <c r="P12" s="9">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>56.4</v>
+        <v>10.4</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>63.4</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>44440</v>
+        <v>44470</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>17</v>
@@ -1824,39 +1824,39 @@
         <v>17</v>
       </c>
       <c r="H13" s="9">
-        <v>1.26</v>
-      </c>
-      <c r="I13" s="8">
-        <v>15.9</v>
-      </c>
-      <c r="J13" s="8">
-        <v>30.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="I13" s="10">
+        <v>3.56</v>
+      </c>
+      <c r="J13" s="10">
+        <v>42</v>
       </c>
       <c r="K13" s="9">
-        <v>7.73</v>
-      </c>
-      <c r="L13" s="8">
-        <v>59.2</v>
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="L13" s="10">
+        <v>56.4</v>
       </c>
       <c r="M13" s="9">
-        <v>1.26</v>
-      </c>
-      <c r="N13" s="8">
-        <v>15.9</v>
-      </c>
-      <c r="O13" s="8">
-        <v>30.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="N13" s="10">
+        <v>3.56</v>
+      </c>
+      <c r="O13" s="10">
+        <v>42</v>
       </c>
       <c r="P13" s="9">
-        <v>7.73</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>59.2</v>
+        <v>9.0299999999999994</v>
+      </c>
+      <c r="Q13" s="10">
+        <v>56.4</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>44409</v>
+        <v>44440</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>17</v>
@@ -1877,33 +1877,86 @@
         <v>17</v>
       </c>
       <c r="H14" s="9">
+        <v>1.26</v>
+      </c>
+      <c r="I14" s="10">
+        <v>15.9</v>
+      </c>
+      <c r="J14" s="10">
+        <v>30.8</v>
+      </c>
+      <c r="K14" s="9">
+        <v>7.73</v>
+      </c>
+      <c r="L14" s="10">
+        <v>59.2</v>
+      </c>
+      <c r="M14" s="9">
+        <v>1.26</v>
+      </c>
+      <c r="N14" s="10">
+        <v>15.9</v>
+      </c>
+      <c r="O14" s="10">
+        <v>30.8</v>
+      </c>
+      <c r="P14" s="9">
+        <v>7.73</v>
+      </c>
+      <c r="Q14" s="10">
+        <v>59.2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+      <c r="A15" s="6">
+        <v>44409</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="9">
         <v>1.0900000000000001</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="J14" s="8">
+      <c r="J15" s="10">
         <v>61.3</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K15" s="9">
         <v>6.47</v>
       </c>
-      <c r="L14" s="8">
+      <c r="L15" s="10">
         <v>66.2</v>
       </c>
-      <c r="M14" s="9">
+      <c r="M15" s="9">
         <v>1.0900000000000001</v>
       </c>
-      <c r="N14" s="9" t="s">
+      <c r="N15" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="O14" s="8">
+      <c r="O15" s="10">
         <v>61.3</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P15" s="9">
         <v>6.47</v>
       </c>
-      <c r="Q14" s="8">
+      <c r="Q15" s="10">
         <v>66.2</v>
       </c>
     </row>
